--- a/output/2026-09-20_10_Croazia_Vukovarsko-srijemska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-20_10_Croazia_Vukovarsko-srijemska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sede legale registrata a Zagabria (Ul. Mirka Viriusa 2); poslovnica attiva a Vukovar dal 2015, Ul. Kriva Bara 1 (già indicata anche come Ul. Kardinala Alojzija Stepinca 24). Email trovata è generale aziendale, non specifica per la filiale.</t>
+          <t>Sede legale registrata a Zagabria (Ul. Mirka Viriusa 2); poslovnica attiva a Vukovar dal 2015, Ul. Kriva Bara 1 (già indicata anche come Ul. Kardinala Alojzija Stepinca 24). Email trovata è generale aziendale, non specifica per la filiale. [DUPLICATO — vedi anche: 2026-09-20_05_Croazia_Vukovarsko-srijemska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Negozio (željezarija) con due punti vendita a Vinkovci (Ul. Hansa Dietricha Genschera 40 e Ulica Hrvatskih kraljeva 9/11a). Ragione sociale legale esatta non confermata con certezza (fonti discordanti citano possibile collegamento a Hidraulika-Flex d.o.o. o a Grupa Kolor) - verificare OIB/ragione sociale al primo contatto.</t>
+          <t>Negozio (željezarija) con due punti vendita a Vinkovci (Ul. Hansa Dietricha Genschera 40 e Ulica Hrvatskih kraljeva 9/11a). Ragione sociale legale esatta non confermata con certezza (fonti discordanti citano possibile collegamento a Hidraulika-Flex d.o.o. o a Grupa Kolor) - verificare OIB/ragione sociale al primo contatto. [DUPLICATO — vedi anche: 2026-09-20_06_Croazia_Vukovarsko-srijemska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -583,7 +583,6 @@
           <t>Bonus Trgovina d.o.o.</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Vinkovci, Vukovarsko-srijemska županija</t>

--- a/output/2026-09-20_10_Croazia_Vukovarsko-srijemska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-20_10_Croazia_Vukovarsko-srijemska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ATTENZIONE: attività camerale principale registrata è riparazione/manutenzione elettrodomestici e attrezzature casa/giardino (T95220), non distribuzione. Sito conferma comunque vendita di utensili/motori/pompe oltre al servizio. Da verificare se operi come rivenditore B2B o prevalentemente come centro assistenza.</t>
+          <t>ATTENZIONE: attività camerale principale registrata è riparazione/manutenzione elettrodomestici e attrezzature casa/giardino (T95220), non distribuzione. Sito conferma comunque vendita di utensili/motori/pompe oltre al servizio. Da verificare se operi come rivenditore B2B o prevalentemente come centro assistenza. [DUPLICATO — vedi anche: 2026-09-20_06_Croazia_Vukovarsko-srijemska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
